--- a/data/再保最低资本2026Q1-0901.xlsx
+++ b/data/再保最低资本2026Q1-0901.xlsx
@@ -1023,6 +1023,9 @@
       <c r="P10" t="n">
         <v>1135442</v>
       </c>
+      <c r="Q10" t="n">
+        <v>778673.86</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1339,6 +1342,9 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>73867.84</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1908,6 +1914,9 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0</v>
       </c>
     </row>
